--- a/data/Diccionario_TFM_Completo.xlsx
+++ b/data/Diccionario_TFM_Completo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\hypertension_management_AI_driven_tool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCEE58F-1CFD-4B21-8A60-5EF90A0691B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF82A2B-6099-478F-8406-7931BBCDA16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="4100" windowWidth="19200" windowHeight="11180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -101,9 +101,6 @@
     <t>RIAGENDR</t>
   </si>
   <si>
-    <t>Género</t>
-  </si>
-  <si>
     <t>Género del participante</t>
   </si>
   <si>
@@ -161,9 +158,6 @@
     <t>DMDBORN4</t>
   </si>
   <si>
-    <t>País Nacimiento</t>
-  </si>
-  <si>
     <t>País de nacimiento</t>
   </si>
   <si>
@@ -173,9 +167,6 @@
     <t>DMDHHSIZ</t>
   </si>
   <si>
-    <t>Tamaño Hogar</t>
-  </si>
-  <si>
     <t>Personas en el hogar</t>
   </si>
   <si>
@@ -269,9 +260,6 @@
     <t>DSDANCNT</t>
   </si>
   <si>
-    <t>Total Antiácidos</t>
-  </si>
-  <si>
     <t>Número de antiácidos tomados</t>
   </si>
   <si>
@@ -293,9 +281,6 @@
     <t>DSD010AN</t>
   </si>
   <si>
-    <t>Uso Antiácidos</t>
-  </si>
-  <si>
     <t>¿Tomó antiácidos 30 días?</t>
   </si>
   <si>
@@ -368,9 +353,6 @@
     <t>BAQ140</t>
   </si>
   <si>
-    <t>Caídas</t>
-  </si>
-  <si>
     <t>Caídas en el último año</t>
   </si>
   <si>
@@ -521,9 +503,6 @@
     <t>BPXOSY1</t>
   </si>
   <si>
-    <t>Sistólica 1</t>
-  </si>
-  <si>
     <t>1ª presión sistólica</t>
   </si>
   <si>
@@ -533,9 +512,6 @@
     <t>BPXODI1</t>
   </si>
   <si>
-    <t>Diastólica 1</t>
-  </si>
-  <si>
     <t>1ª presión diastólica</t>
   </si>
   <si>
@@ -545,9 +521,6 @@
     <t>BPXOSY2</t>
   </si>
   <si>
-    <t>Sistólica 2</t>
-  </si>
-  <si>
     <t>2ª presión sistólica</t>
   </si>
   <si>
@@ -557,27 +530,18 @@
     <t>BPXODI2</t>
   </si>
   <si>
-    <t>Diastólica 2</t>
-  </si>
-  <si>
     <t>2ª presión diastólica</t>
   </si>
   <si>
     <t>BPXOSY3</t>
   </si>
   <si>
-    <t>Sistólica 3</t>
-  </si>
-  <si>
     <t>3ª presión sistólica</t>
   </si>
   <si>
     <t>BPXODI3</t>
   </si>
   <si>
-    <t>Diastólica 3</t>
-  </si>
-  <si>
     <t>3ª presión diastólica</t>
   </si>
   <si>
@@ -689,9 +653,6 @@
     <t>BMXARMC</t>
   </si>
   <si>
-    <t>Perím. Brazo</t>
-  </si>
-  <si>
     <t>Circunferencia brazo</t>
   </si>
   <si>
@@ -719,9 +680,6 @@
     <t>LUAXSTAT</t>
   </si>
   <si>
-    <t>Estado Hígado</t>
-  </si>
-  <si>
     <t>1: Comp, 2: Parcial, 3: Ineligible, 4: No realizado</t>
   </si>
   <si>
@@ -740,9 +698,6 @@
     <t>LUANMVGP</t>
   </si>
   <si>
-    <t>Med. Válidas</t>
-  </si>
-  <si>
     <t>Número mediciones válidas</t>
   </si>
   <si>
@@ -824,9 +779,6 @@
     <t>URXUMA</t>
   </si>
   <si>
-    <t>Albúmina Orina</t>
-  </si>
-  <si>
     <t>Albúmina urinaria</t>
   </si>
   <si>
@@ -848,9 +800,6 @@
     <t>URDUMALC</t>
   </si>
   <si>
-    <t>Com. Albúmina</t>
-  </si>
-  <si>
     <t>Código comentario</t>
   </si>
   <si>
@@ -911,9 +860,6 @@
     <t>LBXHSCRP</t>
   </si>
   <si>
-    <t>Proteína C</t>
-  </si>
-  <si>
     <t>Proteína C-reactiva</t>
   </si>
   <si>
@@ -962,21 +908,12 @@
     <t>LBXNEPCT</t>
   </si>
   <si>
-    <t>% Neutrófilos</t>
-  </si>
-  <si>
     <t>LBXEOPCT</t>
   </si>
   <si>
-    <t>% Eosinófilos</t>
-  </si>
-  <si>
     <t>LBXBAPCT</t>
   </si>
   <si>
-    <t>% Basófilos</t>
-  </si>
-  <si>
     <t>LBDLYMNO</t>
   </si>
   <si>
@@ -995,9 +932,6 @@
     <t>LBDNENO</t>
   </si>
   <si>
-    <t>Neutrófilos Abs</t>
-  </si>
-  <si>
     <t>LBDEONO</t>
   </si>
   <si>
@@ -1007,9 +941,6 @@
     <t>LBDBANO</t>
   </si>
   <si>
-    <t>Basófilos Abs</t>
-  </si>
-  <si>
     <t>LBXRBCSI</t>
   </si>
   <si>
@@ -1127,9 +1058,6 @@
     <t>LBXTLG</t>
   </si>
   <si>
-    <t>Triglicéridos</t>
-  </si>
-  <si>
     <t>Triglicéridos suero</t>
   </si>
   <si>
@@ -1344,6 +1272,78 @@
   </si>
   <si>
     <t>Num. Categóricas</t>
+  </si>
+  <si>
+    <t>Genero</t>
+  </si>
+  <si>
+    <t>Pais Nacimiento</t>
+  </si>
+  <si>
+    <t>Tamano Hogar</t>
+  </si>
+  <si>
+    <t>Total Antiacidos</t>
+  </si>
+  <si>
+    <t>Uso Antiacidos</t>
+  </si>
+  <si>
+    <t>Caidas</t>
+  </si>
+  <si>
+    <t>Sistolica 1</t>
+  </si>
+  <si>
+    <t>Diastolica 1</t>
+  </si>
+  <si>
+    <t>Sistolica 2</t>
+  </si>
+  <si>
+    <t>Diastolica 2</t>
+  </si>
+  <si>
+    <t>Sistolica 3</t>
+  </si>
+  <si>
+    <t>Diastolica 3</t>
+  </si>
+  <si>
+    <t>Perim. Brazo</t>
+  </si>
+  <si>
+    <t>Estado Higado</t>
+  </si>
+  <si>
+    <t>Med. Validas</t>
+  </si>
+  <si>
+    <t>Albumina Orina</t>
+  </si>
+  <si>
+    <t>Com. Albumina</t>
+  </si>
+  <si>
+    <t>Proteina C</t>
+  </si>
+  <si>
+    <t>% Neutrofilos</t>
+  </si>
+  <si>
+    <t>% Eosinofilos</t>
+  </si>
+  <si>
+    <t>% Basofilos</t>
+  </si>
+  <si>
+    <t>Neutrofilos Abs</t>
+  </si>
+  <si>
+    <t>Basofilos Abs</t>
+  </si>
+  <si>
+    <t>Trigliceridos</t>
   </si>
 </sst>
 </file>
@@ -2090,16 +2090,16 @@
         <v>21</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -2107,19 +2107,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -2127,19 +2127,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -2147,19 +2147,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="D8" s="10" t="s">
         <v>34</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>35</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -2167,19 +2167,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -2187,19 +2187,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>43</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -2207,19 +2207,19 @@
         <v>6</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -2227,19 +2227,19 @@
         <v>6</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -2247,19 +2247,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -2267,19 +2267,19 @@
         <v>6</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -2287,19 +2287,19 @@
         <v>6</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -2307,2224 +2307,2224 @@
         <v>6</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>64</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="E17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>86</v>
+        <v>417</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>93</v>
-      </c>
       <c r="C23" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>111</v>
+        <v>418</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="8" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B42" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>158</v>
-      </c>
       <c r="D42" s="10" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>162</v>
+        <v>419</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="8" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>166</v>
+        <v>420</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>170</v>
+        <v>421</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>174</v>
+        <v>422</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>177</v>
+        <v>423</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="8" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>180</v>
+        <v>424</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="8" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E50" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="8" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="11" t="s">
         <v>193</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="E55" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="8" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="8" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>218</v>
+        <v>425</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="8" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="E60" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>228</v>
+        <v>426</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="8" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>235</v>
+        <v>427</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="8" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="C65" s="6" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="8" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="8" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="8" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>263</v>
+        <v>428</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="8" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>271</v>
+        <v>429</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B74" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="B74" s="9" t="s">
-        <v>278</v>
-      </c>
       <c r="C74" s="10" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="8" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="8" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>292</v>
+        <v>430</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>309</v>
+        <v>431</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>311</v>
+        <v>432</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>313</v>
+        <v>433</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C87" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="B87" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>318</v>
-      </c>
       <c r="D87" s="6" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>324</v>
+        <v>435</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>326</v>
+        <v>303</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>328</v>
+        <v>305</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>329</v>
+        <v>306</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>331</v>
+        <v>308</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>332</v>
+        <v>309</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>334</v>
+        <v>311</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>335</v>
+        <v>312</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>336</v>
+        <v>313</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>339</v>
+        <v>316</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>341</v>
+        <v>318</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>332</v>
+        <v>309</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>343</v>
+        <v>320</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>347</v>
+        <v>324</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>350</v>
+        <v>327</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>351</v>
+        <v>328</v>
       </c>
       <c r="E98" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>352</v>
+        <v>329</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>353</v>
+        <v>330</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>354</v>
+        <v>331</v>
       </c>
       <c r="E99" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="8" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>357</v>
+        <v>334</v>
       </c>
       <c r="E100" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>358</v>
+        <v>335</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>360</v>
+        <v>337</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>361</v>
+        <v>338</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="8" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>364</v>
+        <v>436</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="E102" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="8" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="E104" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="8" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="E107" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="D108" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="B108" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="D108" s="10" t="s">
-        <v>383</v>
-      </c>
       <c r="E108" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F108" s="11" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="E109" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="8" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="E110" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>391</v>
+        <v>367</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="8" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F112" s="11" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="8" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="E115" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="8" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F116" s="11" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="8" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="E118" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F118" s="11" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="E119" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="8" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>417</v>
+        <v>393</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="D120" s="10" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>15</v>
       </c>
       <c r="F120" s="11" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="8" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="D122" s="10" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="E123" s="6" t="s">
         <v>15</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="8" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="E125" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="18" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="B126" s="21" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="E126" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F126" s="13" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="23.5" x14ac:dyDescent="0.35">
       <c r="A127" s="19" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="B127" s="24">
         <f>COUNTIF(E:E,E97)</f>
@@ -4533,7 +4533,7 @@
     </row>
     <row r="128" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="20" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="B128" s="23">
         <f>COUNTIF(E:E,E3)</f>

--- a/data/Diccionario_TFM_Completo.xlsx
+++ b/data/Diccionario_TFM_Completo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\hypertension_management_AI_driven_tool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38BBC448-641E-4967-BAEA-52CA53FED0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36736746-4D8B-4774-812D-8D0BEAC80311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="452">
   <si>
     <t>Bloque</t>
   </si>
@@ -282,9 +282,6 @@
   </si>
   <si>
     <t>BAXPF11</t>
-  </si>
-  <si>
-    <t>1: Pasa, 2: Falla</t>
   </si>
   <si>
     <t>BAXTC11</t>
@@ -2149,7 +2146,7 @@
         <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E3" s="19" t="s">
         <v>14</v>
@@ -2166,7 +2163,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
@@ -2186,7 +2183,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>20</v>
@@ -2206,7 +2203,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>23</v>
@@ -2226,7 +2223,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
@@ -2246,7 +2243,7 @@
         <v>28</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>29</v>
@@ -2266,10 +2263,10 @@
         <v>31</v>
       </c>
       <c r="C9" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>14</v>
@@ -2286,7 +2283,7 @@
         <v>33</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>34</v>
@@ -2295,7 +2292,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -2306,7 +2303,7 @@
         <v>35</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>36</v>
@@ -2326,10 +2323,10 @@
         <v>38</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>240</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>10</v>
@@ -2346,10 +2343,10 @@
         <v>40</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E13" s="19" t="s">
         <v>10</v>
@@ -2366,10 +2363,10 @@
         <v>41</v>
       </c>
       <c r="C14" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>244</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>10</v>
@@ -2389,7 +2386,7 @@
         <v>44</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E15" s="19" t="s">
         <v>10</v>
@@ -2406,10 +2403,10 @@
         <v>46</v>
       </c>
       <c r="C16" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>247</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>10</v>
@@ -2426,10 +2423,10 @@
         <v>49</v>
       </c>
       <c r="C17" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="E17" s="19" t="s">
         <v>10</v>
@@ -2446,10 +2443,10 @@
         <v>51</v>
       </c>
       <c r="C18" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>251</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>10</v>
@@ -2466,10 +2463,10 @@
         <v>53</v>
       </c>
       <c r="C19" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>10</v>
@@ -2486,16 +2483,16 @@
         <v>55</v>
       </c>
       <c r="C20" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="24" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
@@ -2506,16 +2503,16 @@
         <v>57</v>
       </c>
       <c r="C21" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="E21" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -2526,16 +2523,16 @@
         <v>59</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E22" s="10" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
@@ -2546,10 +2543,10 @@
         <v>61</v>
       </c>
       <c r="C23" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="E23" s="19" t="s">
         <v>14</v>
@@ -2566,7 +2563,7 @@
         <v>63</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>64</v>
@@ -2586,7 +2583,7 @@
         <v>66</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>67</v>
@@ -2606,7 +2603,7 @@
         <v>68</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>69</v>
@@ -2615,7 +2612,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="24" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
@@ -2626,7 +2623,7 @@
         <v>70</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>71</v>
@@ -2646,7 +2643,7 @@
         <v>72</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>73</v>
@@ -2655,7 +2652,7 @@
         <v>14</v>
       </c>
       <c r="F28" s="24" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
@@ -2666,7 +2663,7 @@
         <v>74</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>75</v>
@@ -2686,7 +2683,7 @@
         <v>76</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>77</v>
@@ -2706,7 +2703,7 @@
         <v>78</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>79</v>
@@ -2726,7 +2723,7 @@
         <v>80</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>81</v>
@@ -2746,16 +2743,16 @@
         <v>82</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F33" s="23" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -2763,19 +2760,19 @@
         <v>58</v>
       </c>
       <c r="B34" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="24" t="s">
         <v>84</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="24" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
@@ -2783,19 +2780,19 @@
         <v>58</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F35" s="23" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -2803,19 +2800,19 @@
         <v>58</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F36" s="24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
@@ -2823,19 +2820,19 @@
         <v>58</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E37" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F37" s="23" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -2843,19 +2840,19 @@
         <v>58</v>
       </c>
       <c r="B38" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="24" t="s">
         <v>89</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="24" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
@@ -2863,19 +2860,19 @@
         <v>58</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E39" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F39" s="23" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -2883,430 +2880,430 @@
         <v>58</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C40" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="E40" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F40" s="24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B41" s="14" t="s">
-        <v>94</v>
-      </c>
       <c r="C41" s="19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E41" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F41" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>14</v>
       </c>
       <c r="F42" s="24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B43" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="23" t="s">
         <v>98</v>
-      </c>
-      <c r="C43" s="19" t="s">
-        <v>287</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E43" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="23" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B44" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="24" t="s">
         <v>100</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="24" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B45" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="23" t="s">
         <v>102</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="23" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E47" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F48" s="24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B49" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="23" t="s">
         <v>107</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="23" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B50" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="24" t="s">
         <v>109</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="24" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E51" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B52" s="11" t="s">
-        <v>113</v>
-      </c>
       <c r="C52" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>305</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>306</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>14</v>
       </c>
       <c r="F52" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B53" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C53" s="19" t="s">
-        <v>308</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="E53" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="23" t="s">
         <v>115</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="23" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B54" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="24" t="s">
         <v>117</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="24" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B55" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="23" t="s">
         <v>119</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="E55" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" s="23" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B56" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" s="24" t="s">
         <v>121</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="E56" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" s="24" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C57" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>317</v>
-      </c>
       <c r="E57" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F57" s="23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E58" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F58" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C59" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="E59" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F59" s="23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C60" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>322</v>
-      </c>
       <c r="E60" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F60" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="B61" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B61" s="14" t="s">
-        <v>128</v>
-      </c>
       <c r="C61" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>60</v>
@@ -3315,61 +3312,61 @@
         <v>14</v>
       </c>
       <c r="F61" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B62" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>14</v>
       </c>
       <c r="F62" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B63" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" s="23" t="s">
         <v>133</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E63" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" s="23" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C64" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>328</v>
       </c>
       <c r="E64" s="10" t="s">
         <v>10</v>
@@ -3380,256 +3377,256 @@
     </row>
     <row r="65" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A65" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B65" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="D65" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" s="23" t="s">
         <v>136</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>329</v>
-      </c>
-      <c r="D65" s="33" t="s">
-        <v>330</v>
-      </c>
-      <c r="E65" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" s="23" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B66" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F66" s="24" t="s">
         <v>138</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="E66" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" s="24" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A67" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B67" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="D67" s="33" t="s">
+        <v>333</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" s="23" t="s">
         <v>140</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="D67" s="33" t="s">
-        <v>334</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" s="23" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A68" s="29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B68" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="E68" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" s="24" t="s">
         <v>142</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="E68" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" s="24" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B69" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" s="23" t="s">
         <v>144</v>
-      </c>
-      <c r="C69" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E69" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" s="23" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="B70" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="C70" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" s="24" t="s">
         <v>147</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="E70" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" s="24" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A71" s="28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B71" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" s="23" t="s">
         <v>149</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>341</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E71" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" s="23" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C72" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>14</v>
       </c>
       <c r="F72" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A73" s="28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B73" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F73" s="23" t="s">
         <v>153</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E73" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" s="23" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B74" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F74" s="24" t="s">
         <v>155</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F74" s="24" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A75" s="28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D75" s="33" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E75" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B76" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F76" s="24" t="s">
         <v>158</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" s="24" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A77" s="28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B77" s="14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C77" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="D77" s="33" t="s">
         <v>353</v>
-      </c>
-      <c r="D77" s="33" t="s">
-        <v>354</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>10</v>
@@ -3640,476 +3637,476 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B78" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F78" s="24" t="s">
         <v>161</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F78" s="24" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A79" s="28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C79" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="E79" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="B80" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="C80" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F80" s="24" t="s">
         <v>165</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F80" s="24" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A81" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B81" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="C81" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E81" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81" s="23" t="s">
         <v>167</v>
-      </c>
-      <c r="C81" s="19" t="s">
-        <v>361</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="E81" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F81" s="23" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C82" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>364</v>
-      </c>
       <c r="E82" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A83" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B83" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C83" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>366</v>
-      </c>
       <c r="E83" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F83" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C84" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>368</v>
-      </c>
       <c r="E84" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A85" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B85" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C85" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>370</v>
-      </c>
       <c r="E85" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F85" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C86" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="D86" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="D86" s="9" t="s">
-        <v>372</v>
-      </c>
       <c r="E86" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A87" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C87" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="D87" s="33" t="s">
         <v>373</v>
       </c>
-      <c r="D87" s="33" t="s">
-        <v>374</v>
-      </c>
       <c r="E87" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F87" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C88" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="D88" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="D88" s="9" t="s">
-        <v>376</v>
-      </c>
       <c r="E88" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A89" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C89" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="D89" s="33" t="s">
         <v>377</v>
       </c>
-      <c r="D89" s="33" t="s">
-        <v>378</v>
-      </c>
       <c r="E89" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F89" s="23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C90" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>380</v>
-      </c>
       <c r="E90" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A91" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B91" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C91" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="D91" s="33" t="s">
+        <v>381</v>
+      </c>
+      <c r="E91" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" s="23" t="s">
         <v>178</v>
-      </c>
-      <c r="C91" s="19" t="s">
-        <v>381</v>
-      </c>
-      <c r="D91" s="33" t="s">
-        <v>382</v>
-      </c>
-      <c r="E91" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91" s="23" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B92" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" s="24" t="s">
         <v>180</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>383</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" s="24" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A93" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B93" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C93" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D93" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="E93" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F93" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B94" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" s="24" t="s">
         <v>183</v>
-      </c>
-      <c r="C94" s="10" t="s">
-        <v>387</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F94" s="24" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A95" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C95" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="D95" s="33" t="s">
         <v>389</v>
       </c>
-      <c r="D95" s="33" t="s">
-        <v>390</v>
-      </c>
       <c r="E95" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F95" s="23" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B96" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="24" t="s">
         <v>186</v>
-      </c>
-      <c r="C96" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" s="24" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A97" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B97" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C97" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>394</v>
-      </c>
       <c r="E97" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F97" s="23" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C98" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="D98" s="3" t="s">
-        <v>396</v>
-      </c>
       <c r="E98" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F98" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A99" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B99" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C99" s="19" t="s">
+        <v>396</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="D99" s="2" t="s">
-        <v>398</v>
-      </c>
       <c r="E99" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F99" s="23" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B100" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100" s="24" t="s">
         <v>191</v>
-      </c>
-      <c r="C100" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F100" s="24" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A101" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="B101" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="B101" s="14" t="s">
-        <v>194</v>
-      </c>
       <c r="C101" s="19" t="s">
+        <v>400</v>
+      </c>
+      <c r="D101" s="33" t="s">
         <v>401</v>
-      </c>
-      <c r="D101" s="33" t="s">
-        <v>402</v>
       </c>
       <c r="E101" s="19" t="s">
         <v>10</v>
@@ -4120,507 +4117,507 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C102" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>404</v>
-      </c>
       <c r="E102" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F102" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A103" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B103" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C103" s="19" t="s">
+        <v>404</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E103" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F103" s="23" t="s">
         <v>196</v>
-      </c>
-      <c r="C103" s="19" t="s">
-        <v>405</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="E103" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103" s="23" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A104" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C104" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="D104" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="D104" s="9" t="s">
-        <v>408</v>
-      </c>
       <c r="E104" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F104" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A105" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C105" s="19" t="s">
+        <v>408</v>
+      </c>
+      <c r="D105" s="33" t="s">
         <v>409</v>
       </c>
-      <c r="D105" s="33" t="s">
-        <v>410</v>
-      </c>
       <c r="E105" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F105" s="23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A106" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C106" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="D106" s="9" t="s">
         <v>411</v>
       </c>
-      <c r="D106" s="9" t="s">
-        <v>412</v>
-      </c>
       <c r="E106" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F106" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A107" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B107" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C107" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="D107" s="33" t="s">
         <v>413</v>
       </c>
-      <c r="D107" s="33" t="s">
-        <v>414</v>
-      </c>
       <c r="E107" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F107" s="23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C108" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="D108" s="3" t="s">
-        <v>416</v>
-      </c>
       <c r="E108" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F108" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="31" x14ac:dyDescent="0.35">
       <c r="A109" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B109" s="14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C109" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="D109" s="33" t="s">
         <v>417</v>
       </c>
-      <c r="D109" s="33" t="s">
-        <v>418</v>
-      </c>
       <c r="E109" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F109" s="23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C110" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="D110" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="D110" s="3" t="s">
-        <v>420</v>
-      </c>
       <c r="E110" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F110" s="24" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A111" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C111" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="D111" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D111" s="2" t="s">
-        <v>422</v>
-      </c>
       <c r="E111" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F111" s="23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B112" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F112" s="24" t="s">
         <v>206</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="E112" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F112" s="24" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A113" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C113" s="19" t="s">
+        <v>424</v>
+      </c>
+      <c r="D113" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="D113" s="2" t="s">
-        <v>426</v>
-      </c>
       <c r="E113" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F113" s="23" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C114" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="D114" s="3" t="s">
         <v>427</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>428</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>14</v>
       </c>
       <c r="F114" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A115" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B115" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C115" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E115" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F115" s="23" t="s">
         <v>210</v>
-      </c>
-      <c r="C115" s="19" t="s">
-        <v>429</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="E115" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F115" s="23" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B116" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F116" s="24" t="s">
         <v>212</v>
-      </c>
-      <c r="C116" s="10" t="s">
-        <v>431</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="E116" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F116" s="24" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A117" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B117" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C117" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="E117" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F117" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C118" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="D118" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="D118" s="3" t="s">
-        <v>436</v>
-      </c>
       <c r="E118" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F118" s="24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A119" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B119" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C119" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="D119" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="D119" s="2" t="s">
-        <v>438</v>
-      </c>
       <c r="E119" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F119" s="23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C120" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="D120" s="3" t="s">
         <v>439</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>440</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>14</v>
       </c>
       <c r="F120" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A121" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B121" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C121" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="D121" s="2" t="s">
-        <v>442</v>
-      </c>
       <c r="E121" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F121" s="23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C122" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="D122" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="D122" s="3" t="s">
-        <v>444</v>
-      </c>
       <c r="E122" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F122" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A123" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B123" s="14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C123" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="D123" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="E123" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F123" s="23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="29" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C124" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="D124" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="D124" s="3" t="s">
-        <v>448</v>
-      </c>
       <c r="E124" s="10" t="s">
         <v>10</v>
       </c>
       <c r="F124" s="24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A125" s="28" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B125" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C125" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="D125" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="D125" s="2" t="s">
-        <v>450</v>
-      </c>
       <c r="E125" s="19" t="s">
         <v>10</v>
       </c>
       <c r="F125" s="23" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C126" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="D126" s="4" t="s">
         <v>451</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>452</v>
       </c>
       <c r="E126" s="20" t="s">
         <v>14</v>
       </c>
       <c r="F126" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="23.5" x14ac:dyDescent="0.35">
       <c r="A127" s="31" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B127" s="7">
         <f>COUNTIF(E:E,E97)</f>
@@ -4629,7 +4626,7 @@
     </row>
     <row r="128" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B128" s="6">
         <f>COUNTIF(E:E,E3)</f>

--- a/data/Diccionario_TFM_Completo.xlsx
+++ b/data/Diccionario_TFM_Completo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\GitHub\hypertension_management_AI_driven_tool\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36736746-4D8B-4774-812D-8D0BEAC80311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91093F7A-F04B-46C8-B10D-19378F4407B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="455">
   <si>
     <t>Bloque</t>
   </si>
@@ -1389,6 +1389,15 @@
   </si>
   <si>
     <t>Código de comentario sobre el manganeso</t>
+  </si>
+  <si>
+    <t>hipertension</t>
+  </si>
+  <si>
+    <t>Target que clasifica a pacientes según la presión arterial media</t>
+  </si>
+  <si>
+    <t>0: Normal, 1: Hipertenso</t>
   </si>
 </sst>
 </file>
@@ -1453,7 +1462,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1636,21 +1645,6 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1672,13 +1666,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1689,16 +1722,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1722,7 +1749,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1737,9 +1764,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1750,9 +1774,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1773,11 +1794,36 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2083,2558 +2129,2574 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="46.81640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.81640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.81640625" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="53.26953125" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.81640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="53.26953125" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="22" t="s">
+      <c r="E2" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="8"/>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="17" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="20" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>228</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="21" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="28" t="s">
+      <c r="A5" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="17" t="s">
         <v>231</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="20" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>232</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="24" t="s">
+      <c r="E6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="17" t="s">
         <v>233</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="20" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>234</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="21" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="17" t="s">
         <v>229</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="20" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="21" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="17" t="s">
         <v>235</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="23" t="s">
+      <c r="E11" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="20" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="24" t="s">
+      <c r="E12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="31" x14ac:dyDescent="0.35">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="E13" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="23" t="s">
+      <c r="E13" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="20" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="8" t="s">
         <v>242</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="24" t="s">
+      <c r="E14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="21" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="17" t="s">
         <v>44</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E15" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="23" t="s">
+      <c r="E15" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="20" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="24" t="s">
+      <c r="E16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="21" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="17" t="s">
         <v>247</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E17" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="23" t="s">
+      <c r="E17" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="20" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="8" t="s">
         <v>249</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="24" t="s">
+      <c r="E18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="21" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="17" t="s">
         <v>251</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="E19" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="23" t="s">
+      <c r="E19" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="20" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>253</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F20" s="24" t="s">
+      <c r="F20" s="21" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="17" t="s">
         <v>255</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="23" t="s">
+      <c r="F21" s="20" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="8" t="s">
         <v>226</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="21" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="17" t="s">
         <v>257</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="20" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="8" t="s">
         <v>268</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F24" s="24" t="s">
+      <c r="F24" s="21" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="17" t="s">
         <v>267</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F25" s="23" t="s">
+      <c r="F25" s="20" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="8" t="s">
         <v>266</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F26" s="24" t="s">
+      <c r="F26" s="21" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="17" t="s">
         <v>265</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="E27" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F27" s="23" t="s">
+      <c r="F27" s="20" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="8" t="s">
         <v>264</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F28" s="24" t="s">
+      <c r="F28" s="21" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="17" t="s">
         <v>263</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F29" s="23" t="s">
+      <c r="F29" s="20" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>262</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F30" s="24" t="s">
+      <c r="F30" s="21" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="17" t="s">
         <v>261</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F31" s="23" t="s">
+      <c r="F31" s="20" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="29" t="s">
+      <c r="A32" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="8" t="s">
         <v>260</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F32" s="24" t="s">
+      <c r="F32" s="21" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="17" t="s">
         <v>269</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E33" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F33" s="23" t="s">
+      <c r="F33" s="20" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="8" t="s">
         <v>277</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="24" t="s">
+      <c r="E34" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="21" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="17" t="s">
         <v>270</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F35" s="23" t="s">
+      <c r="F35" s="20" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="8" t="s">
         <v>278</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E36" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="24" t="s">
+      <c r="E36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="21" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="17" t="s">
         <v>271</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="E37" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F37" s="23" t="s">
+      <c r="F37" s="20" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="8" t="s">
         <v>279</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E38" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="24" t="s">
+      <c r="E38" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="21" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="28" t="s">
+      <c r="A39" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="17" t="s">
         <v>272</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F39" s="23" t="s">
+      <c r="F39" s="20" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="29" t="s">
+      <c r="A40" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="8" t="s">
         <v>280</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E40" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="24" t="s">
+      <c r="E40" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="21" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="17" t="s">
         <v>282</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="E41" s="19" t="s">
+      <c r="E41" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F41" s="23" t="s">
+      <c r="F41" s="20" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A42" s="29" t="s">
+      <c r="A42" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F42" s="24" t="s">
+      <c r="F42" s="21" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="C43" s="17" t="s">
         <v>286</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="E43" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="23" t="s">
+      <c r="E43" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="20" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="29" t="s">
+      <c r="A44" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="8" t="s">
         <v>289</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="E44" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="24" t="s">
+      <c r="E44" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="21" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="28" t="s">
+      <c r="A45" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C45" s="19" t="s">
+      <c r="C45" s="17" t="s">
         <v>287</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="E45" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="23" t="s">
+      <c r="E45" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="20" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="29" t="s">
+      <c r="A46" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="8" t="s">
         <v>290</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="E46" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="24" t="s">
+      <c r="E46" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="21" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="28" t="s">
+      <c r="A47" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="17" t="s">
         <v>288</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="E47" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="23" t="s">
+      <c r="E47" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="20" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="29" t="s">
+      <c r="A48" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="8" t="s">
         <v>291</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="E48" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="24" t="s">
+      <c r="E48" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="21" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="28" t="s">
+      <c r="A49" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B49" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C49" s="19" t="s">
+      <c r="C49" s="17" t="s">
         <v>298</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E49" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="23" t="s">
+      <c r="E49" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="20" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" s="29" t="s">
+      <c r="A50" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="8" t="s">
         <v>299</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="E50" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="24" t="s">
+      <c r="E50" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="21" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="28" t="s">
+      <c r="A51" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C51" s="17" t="s">
         <v>300</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="E51" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="23" t="s">
+      <c r="E51" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="20" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" s="29" t="s">
+      <c r="A52" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C52" s="8" t="s">
         <v>304</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F52" s="24" t="s">
+      <c r="F52" s="21" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="28" t="s">
+      <c r="A53" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="C53" s="19" t="s">
+      <c r="C53" s="17" t="s">
         <v>307</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E53" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="23" t="s">
+      <c r="E53" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="20" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" s="29" t="s">
+      <c r="A54" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="8" t="s">
         <v>308</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="E54" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="24" t="s">
+      <c r="E54" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="21" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="28" t="s">
+      <c r="A55" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="17" t="s">
         <v>311</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="E55" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55" s="23" t="s">
+      <c r="E55" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="20" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C56" s="8" t="s">
         <v>312</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E56" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" s="24" t="s">
+      <c r="E56" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" s="21" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="28" t="s">
+      <c r="A57" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="B57" s="14" t="s">
+      <c r="B57" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C57" s="17" t="s">
         <v>315</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="E57" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F57" s="23" t="s">
+      <c r="E57" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="20" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" s="29" t="s">
+      <c r="A58" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" s="8" t="s">
         <v>314</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="E58" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" s="24" t="s">
+      <c r="E58" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" s="21" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="28" t="s">
+      <c r="A59" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="C59" s="19" t="s">
+      <c r="C59" s="17" t="s">
         <v>318</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="E59" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" s="23" t="s">
+      <c r="E59" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" s="20" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" s="29" t="s">
+      <c r="A60" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C60" s="8" t="s">
         <v>320</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="E60" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" s="24" t="s">
+      <c r="E60" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F60" s="21" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="28" t="s">
+      <c r="A61" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="C61" s="19" t="s">
+      <c r="C61" s="17" t="s">
         <v>322</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E61" s="19" t="s">
+      <c r="E61" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F61" s="23" t="s">
+      <c r="F61" s="20" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" s="29" t="s">
+      <c r="A62" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" s="8" t="s">
         <v>323</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="E62" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F62" s="24" t="s">
+      <c r="F62" s="21" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="28" t="s">
+      <c r="A63" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="14" t="s">
+      <c r="B63" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C63" s="17" t="s">
         <v>324</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="E63" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" s="23" t="s">
+      <c r="E63" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" s="20" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C64" s="10" t="s">
+      <c r="C64" s="8" t="s">
         <v>326</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E64" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F64" s="24" t="s">
+      <c r="E64" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F64" s="21" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A65" s="28" t="s">
+      <c r="A65" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B65" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C65" s="19" t="s">
+      <c r="C65" s="17" t="s">
         <v>328</v>
       </c>
-      <c r="D65" s="33" t="s">
+      <c r="D65" s="28" t="s">
         <v>329</v>
       </c>
-      <c r="E65" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" s="23" t="s">
+      <c r="E65" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" s="20" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A66" s="29" t="s">
+      <c r="A66" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="C66" s="8" t="s">
         <v>330</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="E66" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F66" s="24" t="s">
+      <c r="E66" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F66" s="21" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A67" s="28" t="s">
+      <c r="A67" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="B67" s="14" t="s">
+      <c r="B67" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="C67" s="19" t="s">
+      <c r="C67" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="D67" s="33" t="s">
+      <c r="D67" s="28" t="s">
         <v>333</v>
       </c>
-      <c r="E67" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" s="23" t="s">
+      <c r="E67" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" s="20" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A68" s="29" t="s">
+      <c r="A68" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="C68" s="10" t="s">
+      <c r="C68" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="D68" s="9" t="s">
+      <c r="D68" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="E68" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" s="24" t="s">
+      <c r="E68" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" s="21" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A69" s="28" t="s">
+      <c r="A69" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="C69" s="19" t="s">
+      <c r="C69" s="17" t="s">
         <v>336</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="E69" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" s="23" t="s">
+      <c r="E69" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" s="20" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" s="29" t="s">
+      <c r="A70" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="C70" s="10" t="s">
+      <c r="C70" s="8" t="s">
         <v>338</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="E70" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" s="24" t="s">
+      <c r="E70" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" s="21" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="28" t="s">
+      <c r="A71" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="B71" s="14" t="s">
+      <c r="B71" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="C71" s="19" t="s">
+      <c r="C71" s="17" t="s">
         <v>340</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="E71" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" s="23" t="s">
+      <c r="E71" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" s="20" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A72" s="29" t="s">
+      <c r="A72" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="C72" s="8" t="s">
         <v>342</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="E72" s="10" t="s">
+      <c r="E72" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F72" s="24" t="s">
+      <c r="F72" s="21" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A73" s="28" t="s">
+      <c r="A73" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="B73" s="14" t="s">
+      <c r="B73" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="C73" s="19" t="s">
+      <c r="C73" s="17" t="s">
         <v>344</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="E73" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" s="23" t="s">
+      <c r="E73" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F73" s="20" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="29" t="s">
+      <c r="A74" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="C74" s="10" t="s">
+      <c r="C74" s="8" t="s">
         <v>345</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="E74" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F74" s="24" t="s">
+      <c r="E74" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F74" s="21" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A75" s="28" t="s">
+      <c r="A75" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="B75" s="14" t="s">
+      <c r="B75" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C75" s="19" t="s">
+      <c r="C75" s="17" t="s">
         <v>347</v>
       </c>
-      <c r="D75" s="33" t="s">
+      <c r="D75" s="28" t="s">
         <v>349</v>
       </c>
-      <c r="E75" s="19" t="s">
+      <c r="E75" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F75" s="23" t="s">
+      <c r="F75" s="20" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A76" s="29" t="s">
+      <c r="A76" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="C76" s="10" t="s">
+      <c r="C76" s="8" t="s">
         <v>350</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="E76" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F76" s="24" t="s">
+      <c r="E76" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F76" s="21" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A77" s="28" t="s">
+      <c r="A77" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="14" t="s">
+      <c r="B77" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="C77" s="19" t="s">
+      <c r="C77" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="D77" s="33" t="s">
+      <c r="D77" s="28" t="s">
         <v>353</v>
       </c>
-      <c r="E77" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" s="23" t="s">
+      <c r="E77" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F77" s="20" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A78" s="29" t="s">
+      <c r="A78" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="C78" s="8" t="s">
         <v>354</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E78" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F78" s="24" t="s">
+      <c r="E78" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F78" s="21" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A79" s="28" t="s">
+      <c r="A79" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="B79" s="14" t="s">
+      <c r="B79" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="C79" s="19" t="s">
+      <c r="C79" s="17" t="s">
         <v>356</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="E79" s="19" t="s">
+      <c r="E79" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F79" s="23" t="s">
+      <c r="F79" s="20" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" s="29" t="s">
+      <c r="A80" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C80" s="8" t="s">
         <v>358</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="E80" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F80" s="24" t="s">
+      <c r="E80" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F80" s="21" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A81" s="28" t="s">
+      <c r="A81" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B81" s="14" t="s">
+      <c r="B81" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="C81" s="19" t="s">
+      <c r="C81" s="17" t="s">
         <v>360</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="E81" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F81" s="23" t="s">
+      <c r="E81" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F81" s="20" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A82" s="29" t="s">
+      <c r="A82" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="C82" s="8" t="s">
         <v>362</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E82" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F82" s="24" t="s">
+      <c r="E82" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F82" s="21" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A83" s="28" t="s">
+      <c r="A83" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B83" s="14" t="s">
+      <c r="B83" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="C83" s="19" t="s">
+      <c r="C83" s="17" t="s">
         <v>364</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="E83" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F83" s="23" t="s">
+      <c r="E83" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F83" s="20" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A84" s="29" t="s">
+      <c r="A84" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C84" s="8" t="s">
         <v>366</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="E84" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F84" s="24" t="s">
+      <c r="E84" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F84" s="21" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A85" s="28" t="s">
+      <c r="A85" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B85" s="14" t="s">
+      <c r="B85" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="C85" s="19" t="s">
+      <c r="C85" s="17" t="s">
         <v>368</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="E85" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F85" s="23" t="s">
+      <c r="E85" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F85" s="20" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" s="29" t="s">
+      <c r="A86" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="C86" s="10" t="s">
+      <c r="C86" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="D86" s="9" t="s">
+      <c r="D86" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="E86" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" s="24" t="s">
+      <c r="E86" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F86" s="21" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A87" s="28" t="s">
+      <c r="A87" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B87" s="14" t="s">
+      <c r="B87" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="C87" s="19" t="s">
+      <c r="C87" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="D87" s="33" t="s">
+      <c r="D87" s="28" t="s">
         <v>373</v>
       </c>
-      <c r="E87" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F87" s="23" t="s">
+      <c r="E87" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F87" s="20" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A88" s="29" t="s">
+      <c r="A88" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C88" s="10" t="s">
+      <c r="C88" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D88" s="9" t="s">
+      <c r="D88" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="E88" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F88" s="24" t="s">
+      <c r="E88" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" s="21" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A89" s="28" t="s">
+      <c r="A89" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B89" s="14" t="s">
+      <c r="B89" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="C89" s="19" t="s">
+      <c r="C89" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="D89" s="33" t="s">
+      <c r="D89" s="28" t="s">
         <v>377</v>
       </c>
-      <c r="E89" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F89" s="23" t="s">
+      <c r="E89" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" s="20" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A90" s="29" t="s">
+      <c r="A90" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="C90" s="10" t="s">
+      <c r="C90" s="8" t="s">
         <v>378</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="E90" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F90" s="24" t="s">
+      <c r="E90" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F90" s="21" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A91" s="28" t="s">
+      <c r="A91" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B91" s="14" t="s">
+      <c r="B91" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="C91" s="19" t="s">
+      <c r="C91" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="D91" s="33" t="s">
+      <c r="D91" s="28" t="s">
         <v>381</v>
       </c>
-      <c r="E91" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F91" s="23" t="s">
+      <c r="E91" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" s="20" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" s="29" t="s">
+      <c r="A92" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="C92" s="10" t="s">
+      <c r="C92" s="8" t="s">
         <v>382</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E92" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" s="24" t="s">
+      <c r="E92" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" s="21" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A93" s="28" t="s">
+      <c r="A93" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="B93" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="C93" s="19" t="s">
+      <c r="C93" s="17" t="s">
         <v>384</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="E93" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F93" s="23" t="s">
+      <c r="E93" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F93" s="20" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A94" s="29" t="s">
+      <c r="A94" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="C94" s="10" t="s">
+      <c r="C94" s="8" t="s">
         <v>386</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="E94" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F94" s="24" t="s">
+      <c r="E94" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" s="21" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A95" s="28" t="s">
+      <c r="A95" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B95" s="14" t="s">
+      <c r="B95" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="C95" s="19" t="s">
+      <c r="C95" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="D95" s="33" t="s">
+      <c r="D95" s="28" t="s">
         <v>389</v>
       </c>
-      <c r="E95" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" s="23" t="s">
+      <c r="E95" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F95" s="20" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A96" s="29" t="s">
+      <c r="A96" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C96" s="10" t="s">
+      <c r="C96" s="8" t="s">
         <v>390</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="E96" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" s="24" t="s">
+      <c r="E96" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="21" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A97" s="28" t="s">
+      <c r="A97" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B97" s="14" t="s">
+      <c r="B97" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="C97" s="19" t="s">
+      <c r="C97" s="17" t="s">
         <v>392</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="E97" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F97" s="23" t="s">
+      <c r="E97" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F97" s="20" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" s="29" t="s">
+      <c r="A98" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="B98" s="11" t="s">
+      <c r="B98" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="C98" s="10" t="s">
+      <c r="C98" s="8" t="s">
         <v>394</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="E98" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" s="24" t="s">
+      <c r="E98" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F98" s="21" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A99" s="28" t="s">
+      <c r="A99" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B99" s="14" t="s">
+      <c r="B99" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="C99" s="19" t="s">
+      <c r="C99" s="17" t="s">
         <v>396</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="E99" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F99" s="23" t="s">
+      <c r="E99" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F99" s="20" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" s="29" t="s">
+      <c r="A100" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="B100" s="11" t="s">
+      <c r="B100" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="C100" s="10" t="s">
+      <c r="C100" s="8" t="s">
         <v>398</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="E100" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F100" s="24" t="s">
+      <c r="E100" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100" s="21" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A101" s="28" t="s">
+      <c r="A101" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B101" s="14" t="s">
+      <c r="B101" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C101" s="19" t="s">
+      <c r="C101" s="17" t="s">
         <v>400</v>
       </c>
-      <c r="D101" s="33" t="s">
+      <c r="D101" s="28" t="s">
         <v>401</v>
       </c>
-      <c r="E101" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F101" s="23" t="s">
+      <c r="E101" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" s="20" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="29" t="s">
+      <c r="A102" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B102" s="11" t="s">
+      <c r="B102" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="C102" s="10" t="s">
+      <c r="C102" s="8" t="s">
         <v>402</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="E102" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F102" s="24" t="s">
+      <c r="E102" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F102" s="21" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A103" s="28" t="s">
+      <c r="A103" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B103" s="14" t="s">
+      <c r="B103" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="C103" s="19" t="s">
+      <c r="C103" s="17" t="s">
         <v>404</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="E103" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103" s="23" t="s">
+      <c r="E103" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F103" s="20" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A104" s="29" t="s">
+      <c r="A104" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B104" s="11" t="s">
+      <c r="B104" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="C104" s="10" t="s">
+      <c r="C104" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="D104" s="9" t="s">
+      <c r="D104" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="E104" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F104" s="24" t="s">
+      <c r="E104" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F104" s="21" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A105" s="28" t="s">
+      <c r="A105" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B105" s="14" t="s">
+      <c r="B105" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="C105" s="19" t="s">
+      <c r="C105" s="17" t="s">
         <v>408</v>
       </c>
-      <c r="D105" s="33" t="s">
+      <c r="D105" s="28" t="s">
         <v>409</v>
       </c>
-      <c r="E105" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F105" s="23" t="s">
+      <c r="E105" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F105" s="20" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="A106" s="29" t="s">
+      <c r="A106" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B106" s="11" t="s">
+      <c r="B106" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="C106" s="10" t="s">
+      <c r="C106" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="D106" s="9" t="s">
+      <c r="D106" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="E106" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F106" s="24" t="s">
+      <c r="E106" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F106" s="21" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A107" s="28" t="s">
+      <c r="A107" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B107" s="14" t="s">
+      <c r="B107" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="C107" s="19" t="s">
+      <c r="C107" s="17" t="s">
         <v>412</v>
       </c>
-      <c r="D107" s="33" t="s">
+      <c r="D107" s="28" t="s">
         <v>413</v>
       </c>
-      <c r="E107" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F107" s="23" t="s">
+      <c r="E107" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F107" s="20" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" s="29" t="s">
+      <c r="A108" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B108" s="11" t="s">
+      <c r="B108" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="C108" s="10" t="s">
+      <c r="C108" s="8" t="s">
         <v>414</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="E108" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F108" s="24" t="s">
+      <c r="E108" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F108" s="21" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A109" s="28" t="s">
+      <c r="A109" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B109" s="14" t="s">
+      <c r="B109" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="C109" s="19" t="s">
+      <c r="C109" s="17" t="s">
         <v>416</v>
       </c>
-      <c r="D109" s="33" t="s">
+      <c r="D109" s="28" t="s">
         <v>417</v>
       </c>
-      <c r="E109" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F109" s="23" t="s">
+      <c r="E109" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F109" s="20" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A110" s="29" t="s">
+      <c r="A110" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B110" s="11" t="s">
+      <c r="B110" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="C110" s="10" t="s">
+      <c r="C110" s="8" t="s">
         <v>418</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="E110" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F110" s="24" t="s">
+      <c r="E110" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F110" s="21" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A111" s="28" t="s">
+      <c r="A111" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B111" s="14" t="s">
+      <c r="B111" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="C111" s="19" t="s">
+      <c r="C111" s="17" t="s">
         <v>420</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="E111" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F111" s="23" t="s">
+      <c r="E111" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F111" s="20" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A112" s="29" t="s">
+      <c r="A112" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B112" s="11" t="s">
+      <c r="B112" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="C112" s="10" t="s">
+      <c r="C112" s="8" t="s">
         <v>422</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="E112" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F112" s="24" t="s">
+      <c r="E112" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F112" s="21" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A113" s="28" t="s">
+      <c r="A113" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B113" s="14" t="s">
+      <c r="B113" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="C113" s="19" t="s">
+      <c r="C113" s="17" t="s">
         <v>424</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="E113" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" s="23" t="s">
+      <c r="E113" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113" s="20" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A114" s="29" t="s">
+      <c r="A114" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B114" s="11" t="s">
+      <c r="B114" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="C114" s="10" t="s">
+      <c r="C114" s="8" t="s">
         <v>426</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="E114" s="10" t="s">
+      <c r="E114" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F114" s="24" t="s">
+      <c r="F114" s="21" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A115" s="28" t="s">
+      <c r="A115" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B115" s="14" t="s">
+      <c r="B115" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="C115" s="19" t="s">
+      <c r="C115" s="17" t="s">
         <v>428</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="E115" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F115" s="23" t="s">
+      <c r="E115" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F115" s="20" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A116" s="29" t="s">
+      <c r="A116" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B116" s="11" t="s">
+      <c r="B116" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="C116" s="10" t="s">
+      <c r="C116" s="8" t="s">
         <v>430</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="E116" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F116" s="24" t="s">
+      <c r="E116" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F116" s="21" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A117" s="28" t="s">
+      <c r="A117" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B117" s="14" t="s">
+      <c r="B117" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="C117" s="19" t="s">
+      <c r="C117" s="17" t="s">
         <v>432</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="E117" s="19" t="s">
+      <c r="E117" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F117" s="23" t="s">
+      <c r="F117" s="20" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A118" s="29" t="s">
+      <c r="A118" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B118" s="11" t="s">
+      <c r="B118" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="C118" s="10" t="s">
+      <c r="C118" s="8" t="s">
         <v>434</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="E118" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F118" s="24" t="s">
+      <c r="E118" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F118" s="21" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A119" s="28" t="s">
+      <c r="A119" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B119" s="14" t="s">
+      <c r="B119" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="C119" s="19" t="s">
+      <c r="C119" s="17" t="s">
         <v>436</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="E119" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F119" s="23" t="s">
+      <c r="E119" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F119" s="20" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A120" s="29" t="s">
+      <c r="A120" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B120" s="11" t="s">
+      <c r="B120" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="C120" s="10" t="s">
+      <c r="C120" s="8" t="s">
         <v>438</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="E120" s="10" t="s">
+      <c r="E120" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F120" s="24" t="s">
+      <c r="F120" s="21" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A121" s="28" t="s">
+      <c r="A121" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B121" s="14" t="s">
+      <c r="B121" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="C121" s="19" t="s">
+      <c r="C121" s="17" t="s">
         <v>440</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="E121" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F121" s="23" t="s">
+      <c r="E121" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F121" s="20" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A122" s="29" t="s">
+      <c r="A122" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B122" s="11" t="s">
+      <c r="B122" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="C122" s="10" t="s">
+      <c r="C122" s="8" t="s">
         <v>442</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="E122" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" s="24" t="s">
+      <c r="E122" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F122" s="21" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A123" s="28" t="s">
+      <c r="A123" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B123" s="14" t="s">
+      <c r="B123" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="C123" s="19" t="s">
+      <c r="C123" s="17" t="s">
         <v>444</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="E123" s="19" t="s">
+      <c r="E123" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F123" s="23" t="s">
+      <c r="F123" s="20" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A124" s="29" t="s">
+      <c r="A124" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B124" s="11" t="s">
+      <c r="B124" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="C124" s="10" t="s">
+      <c r="C124" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="E124" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F124" s="24" t="s">
+      <c r="E124" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F124" s="21" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A125" s="28" t="s">
+      <c r="A125" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="B125" s="14" t="s">
+      <c r="B125" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="C125" s="19" t="s">
+      <c r="C125" s="17" t="s">
         <v>448</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="E125" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F125" s="23" t="s">
+      <c r="E125" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F125" s="20" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A126" s="30" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="B126" s="15" t="s">
+      <c r="B126" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="C126" s="20" t="s">
+      <c r="C126" s="29" t="s">
         <v>450</v>
       </c>
-      <c r="D126" s="4" t="s">
+      <c r="D126" s="30" t="s">
         <v>451</v>
       </c>
-      <c r="E126" s="20" t="s">
+      <c r="E126" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F126" s="25" t="s">
+      <c r="F126" s="31" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A127" s="31" t="s">
+    <row r="127" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A127" s="34"/>
+      <c r="B127" s="34"/>
+      <c r="C127" s="35" t="s">
+        <v>452</v>
+      </c>
+      <c r="D127" s="38" t="s">
+        <v>453</v>
+      </c>
+      <c r="E127" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F127" s="37" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A128" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="B127" s="7">
+      <c r="B128" s="33">
         <f>COUNTIF(E:E,E97)</f>
         <v>88</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="32" t="s">
+    <row r="129" spans="1:2" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A129" s="27" t="s">
         <v>224</v>
       </c>
-      <c r="B128" s="6">
+      <c r="B129" s="5">
         <f>COUNTIF(E:E,E3)</f>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B129" s="16"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B130" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
